--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q20_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009265583338561372</v>
+        <v>0.009307245154256061</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009265583338561372</v>
+        <v>0.009307245154256061</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004000974533396891</v>
+        <v>0.004526674965814974</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.008792786334046955</v>
+        <v>0.008739558948359538</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008792786334046955</v>
+        <v>0.008739558948359538</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003523252161463398</v>
+        <v>0.003801746805392588</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00836544982834872</v>
+        <v>0.008243903234864293</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00836544982834872</v>
+        <v>0.008243903234864293</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00300609013259156</v>
+        <v>0.003219179976078347</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008284054907674056</v>
+        <v>0.008154426907771434</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008284054907674056</v>
+        <v>0.008154426907771434</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0024465878728023</v>
+        <v>0.002642359942849014</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008837434681978952</v>
+        <v>0.008752826211662106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008837434681978952</v>
+        <v>0.008752826211662106</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002148034967463443</v>
+        <v>0.00239365252702623</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01020404995305797</v>
+        <v>0.01020349925430104</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01020404995305797</v>
+        <v>0.01020349925430104</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00217030479588728</v>
+        <v>0.002577683165154473</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0126635097566223</v>
+        <v>0.01277510350847142</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0126635097566223</v>
+        <v>0.01277510350847142</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002207868988152491</v>
+        <v>0.002684599549219047</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01606533799272821</v>
+        <v>0.01629660217123927</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01606533799272821</v>
+        <v>0.01629660217123927</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00229472482009601</v>
+        <v>0.002488900296628342</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02012967830777977</v>
+        <v>0.02045496915292378</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02012967830777977</v>
+        <v>0.02045496915292378</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003350892279062969</v>
+        <v>0.003107477279900011</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02451498876186781</v>
+        <v>0.02487819663128431</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02451498876186781</v>
+        <v>0.02487819663128431</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004586672718380896</v>
+        <v>0.004302155556305812</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02872330989804586</v>
+        <v>0.02906575523582951</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02872330989804586</v>
+        <v>0.02906575523582951</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004180964041489822</v>
+        <v>0.003877938161683166</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03324763297565136</v>
+        <v>0.03356601381444595</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03324763297565136</v>
+        <v>0.03356601381444595</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002327675443434831</v>
+        <v>0.001957427248071852</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03869576811950859</v>
+        <v>0.03904940123514947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03869576811950859</v>
+        <v>0.03904940123514947</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002019524924789494</v>
+        <v>0.002284168462917113</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04480044404868482</v>
+        <v>0.04525812667435348</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04480044404868482</v>
+        <v>0.04525812667435348</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003712917408475706</v>
+        <v>0.004469679116479276</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05073690038192015</v>
+        <v>0.05132890555313275</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05073690038192015</v>
+        <v>0.05132890555313275</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004971954068814283</v>
+        <v>0.006078453879408407</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05559692759688938</v>
+        <v>0.05631353100108585</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05559692759688938</v>
+        <v>0.05631353100108585</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005615620110954579</v>
+        <v>0.0069572021616003</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0597920271577211</v>
+        <v>0.06060256374787754</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0597920271577211</v>
+        <v>0.06060256374787754</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005907501787433511</v>
+        <v>0.007422396865543589</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06272699902883346</v>
+        <v>0.06359027441534711</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06272699902883346</v>
+        <v>0.06359027441534711</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00602189496170004</v>
+        <v>0.00757790643168173</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06465872021827948</v>
+        <v>0.06552727917217051</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06465872021827948</v>
+        <v>0.06552727917217051</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006095168476003482</v>
+        <v>0.007544229203287706</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.06541096286417619</v>
+        <v>0.0662444608134982</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06541096286417619</v>
+        <v>0.0662444608134982</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006094586999814658</v>
+        <v>0.007345185046032745</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06575307547072953</v>
+        <v>0.06653468733061496</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06575307547072953</v>
+        <v>0.06653468733061496</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006183487763085934</v>
+        <v>0.007087315940106764</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06483008032692789</v>
+        <v>0.06555257390957758</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06483008032692789</v>
+        <v>0.06555257390957758</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00614934389515164</v>
+        <v>0.006591396950376272</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06374618969621823</v>
+        <v>0.06442274551557922</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06374618969621823</v>
+        <v>0.06442274551557922</v>
       </c>
       <c r="D24" t="n">
-        <v>0.006017345263756257</v>
+        <v>0.005966168884630447</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06228966253542105</v>
+        <v>0.06294615848055535</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06228966253542105</v>
+        <v>0.06294615848055535</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005748672661152246</v>
+        <v>0.005264252155886372</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06059642361202019</v>
+        <v>0.06124918378493749</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06059642361202019</v>
+        <v>0.06124918378493749</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005475673182870894</v>
+        <v>0.004692217048924982</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.05908629674401934</v>
+        <v>0.0597227480901797</v>
       </c>
       <c r="C27" t="n">
-        <v>0.05908629674401934</v>
+        <v>0.0597227480901797</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005337166013308294</v>
+        <v>0.004319458568814997</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.05659169446568449</v>
+        <v>0.05723146620311607</v>
       </c>
       <c r="C28" t="n">
-        <v>0.05659169446568449</v>
+        <v>0.05723146620311607</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005165004488084505</v>
+        <v>0.004127454094990837</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.05503626590190783</v>
+        <v>0.05567018207218045</v>
       </c>
       <c r="C29" t="n">
-        <v>0.05503626590190783</v>
+        <v>0.05567018207218045</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005168206474153416</v>
+        <v>0.004051576675977102</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.05430477248064063</v>
+        <v>0.05495971771879141</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05430477248064063</v>
+        <v>0.05495971771879141</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005201242868466432</v>
+        <v>0.003986888700356641</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05326749434876947</v>
+        <v>0.05392229822778117</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05326749434876947</v>
+        <v>0.05392229822778117</v>
       </c>
       <c r="D31" t="n">
-        <v>0.005324794482965326</v>
+        <v>0.004046425811047884</v>
       </c>
     </row>
   </sheetData>
